--- a/diseases/d125/2010-2014.xlsx
+++ b/diseases/d125/2010-2014.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28662,7 +28662,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -33706,7 +33706,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -35078,7 +35078,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -39301,7 +39301,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -40525,7 +40525,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -41749,7 +41749,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -44345,7 +44345,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -46941,7 +46941,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -48165,7 +48165,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -49389,7 +49389,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -50761,7 +50761,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -51985,7 +51985,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">

--- a/diseases/d125/2010-2014.xlsx
+++ b/diseases/d125/2010-2014.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28662,7 +28662,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -33706,7 +33706,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -35078,7 +35078,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -39301,7 +39301,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -40525,7 +40525,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -41749,7 +41749,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -44345,7 +44345,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -46941,7 +46941,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -48165,7 +48165,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -49389,7 +49389,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -50761,7 +50761,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -51985,7 +51985,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">

--- a/diseases/d125/2010-2014.xlsx
+++ b/diseases/d125/2010-2014.xlsx
@@ -17105,28 +17105,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -17253,28 +17267,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -17401,28 +17429,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -18181,28 +18223,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -18329,28 +18385,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -18477,28 +18547,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -18625,28 +18709,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -19405,28 +19503,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -19553,28 +19665,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -19701,28 +19827,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -19849,28 +19989,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -19997,28 +20151,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -20777,28 +20945,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20925,28 +21107,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21073,28 +21269,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -21221,28 +21431,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -22404,28 +22628,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -22552,28 +22790,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -22700,28 +22952,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -22848,28 +23114,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -23235,28 +23515,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -23776,28 +24070,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -23924,28 +24232,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -24072,28 +24394,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -24459,28 +24795,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -25000,28 +25350,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -25148,28 +25512,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -25296,28 +25674,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -25444,28 +25836,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -26224,28 +26630,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -26372,28 +26792,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -26520,28 +26954,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -26668,28 +27116,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -27448,28 +27910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -27596,28 +28072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -27744,28 +28234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -27892,28 +28396,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -28040,28 +28558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -28820,28 +29352,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -28968,28 +29514,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -29116,28 +29676,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -29264,28 +29838,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -30044,28 +30632,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -30192,28 +30794,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -30340,28 +30956,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -30488,28 +31118,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -31268,28 +31912,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -31416,28 +32074,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -31564,28 +32236,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -31712,28 +32398,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -31860,28 +32560,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -32640,28 +33354,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -32788,28 +33516,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -32936,28 +33678,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -33084,28 +33840,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -33864,28 +34634,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -34012,28 +34796,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -34160,28 +34958,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -34308,28 +35120,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -34695,28 +35521,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -35236,28 +36076,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -35384,28 +36238,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -35532,28 +36400,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -35680,28 +36562,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -36460,28 +37356,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -36608,28 +37518,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -36756,28 +37680,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -36904,28 +37842,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -38087,28 +39039,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -38235,28 +39201,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -38383,28 +39363,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -38531,28 +39525,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -38679,28 +39687,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -39459,28 +40481,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -39607,28 +40643,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -39755,28 +40805,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -39903,28 +40967,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -40683,28 +41761,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -40831,28 +41923,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -40979,28 +42085,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -41127,28 +42247,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -41907,28 +43041,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -42055,28 +43203,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -42203,28 +43365,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -42351,28 +43527,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -43131,28 +44321,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -43279,28 +44483,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -43427,28 +44645,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -43575,28 +44807,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -43723,28 +44969,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -44503,28 +45763,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -44651,28 +45925,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -44799,28 +46087,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -44947,28 +46249,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
@@ -45727,28 +47043,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
@@ -45875,28 +47205,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
@@ -46023,28 +47367,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
@@ -46171,28 +47529,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -46558,28 +47930,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
@@ -47099,28 +48485,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -47247,28 +48647,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -47395,28 +48809,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -47543,28 +48971,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
@@ -48323,28 +49765,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -48471,28 +49927,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -48619,28 +50089,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -48767,28 +50251,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -49547,28 +51045,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -49695,28 +51207,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -49843,28 +51369,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
@@ -49991,28 +51531,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
@@ -50139,28 +51693,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
@@ -50919,28 +52487,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
@@ -51067,28 +52649,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
@@ -51215,28 +52811,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR279" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
@@ -51363,28 +52973,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR280" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
@@ -52143,28 +53767,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR284" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS284" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
@@ -52291,28 +53929,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR285" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS285" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
@@ -52439,28 +54091,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR286" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS286" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
@@ -52587,28 +54253,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR287" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS287" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
+        </is>
+      </c>
       <c r="AT287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">

--- a/diseases/d125/2010-2014.xlsx
+++ b/diseases/d125/2010-2014.xlsx
@@ -5949,17 +5949,15 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -5967,7 +5965,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5977,12 +5975,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -5992,11 +5985,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6111,17 +6099,15 @@
       <c r="O39" t="n">
         <v>2</v>
       </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0.001563375917999682</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -6129,7 +6115,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6139,12 +6125,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6154,11 +6135,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6273,17 +6249,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -6291,7 +6265,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6301,12 +6275,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6316,11 +6285,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6579,17 +6543,15 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -6597,7 +6559,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6607,12 +6569,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -6622,11 +6579,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6741,17 +6693,15 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -6759,7 +6709,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6769,12 +6719,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -6784,11 +6729,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6903,17 +6843,15 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -6921,7 +6859,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6931,12 +6869,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6946,11 +6879,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7065,17 +6993,15 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -7083,7 +7009,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7093,12 +7019,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7108,11 +7029,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7371,17 +7287,15 @@
       <c r="O47" t="n">
         <v>2</v>
       </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0.001563375917999682</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -7389,7 +7303,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7399,12 +7313,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -7414,11 +7323,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7533,17 +7437,15 @@
       <c r="O48" t="n">
         <v>3</v>
       </c>
+      <c r="P48" t="n">
+        <v>3</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0.002345063876999524</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -7551,7 +7453,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7561,12 +7463,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -7576,11 +7473,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7695,17 +7587,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -7713,7 +7603,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7723,12 +7613,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -7738,11 +7623,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7857,17 +7737,15 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -7875,7 +7753,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7885,12 +7763,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -7900,11 +7773,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8019,17 +7887,15 @@
       <c r="O51" t="n">
         <v>2</v>
       </c>
+      <c r="P51" t="n">
+        <v>2</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0.001563375917999682</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -8037,7 +7903,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8047,12 +7913,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8062,11 +7923,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8325,17 +8181,15 @@
       <c r="O53" t="n">
         <v>4</v>
       </c>
+      <c r="P53" t="n">
+        <v>4</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0.003126751835999364</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -8343,7 +8197,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8353,12 +8207,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -8368,11 +8217,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8487,17 +8331,15 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -8505,7 +8347,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8515,12 +8357,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -8530,11 +8367,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8649,17 +8481,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -8667,7 +8497,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8677,12 +8507,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -8692,11 +8517,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8811,17 +8631,15 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -8829,7 +8647,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8839,12 +8657,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -8854,11 +8667,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9261,17 +9069,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -9279,7 +9085,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9289,12 +9095,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -9304,11 +9105,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9423,17 +9219,15 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
+      <c r="P60" t="n">
+        <v>3</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -9441,7 +9235,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9451,12 +9245,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -9466,11 +9255,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9585,17 +9369,15 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -9603,7 +9385,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9613,12 +9395,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -9628,11 +9405,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9747,17 +9519,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -9765,7 +9535,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9775,12 +9545,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -9790,11 +9555,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9909,17 +9669,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -9927,7 +9685,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9937,12 +9695,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -9952,11 +9705,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10215,17 +9963,15 @@
       <c r="O65" t="n">
         <v>4</v>
       </c>
+      <c r="P65" t="n">
+        <v>4</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -10233,7 +9979,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10243,12 +9989,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -10258,11 +9999,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10377,17 +10113,15 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
+      <c r="P66" t="n">
+        <v>2</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -10395,7 +10129,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10405,12 +10139,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10420,11 +10149,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10539,17 +10263,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -10557,7 +10279,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10567,12 +10289,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -10582,11 +10299,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10701,17 +10413,15 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -10719,7 +10429,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10729,12 +10439,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -10744,11 +10449,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11007,17 +10707,15 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -11025,7 +10723,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11035,12 +10733,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -11050,11 +10743,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11169,17 +10857,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -11187,7 +10873,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11197,12 +10883,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11212,11 +10893,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11331,17 +11007,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -11349,7 +11023,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11359,12 +11033,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11374,11 +11043,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11493,17 +11157,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -11511,7 +11173,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11521,12 +11183,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -11536,11 +11193,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11799,17 +11451,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -11817,7 +11467,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11827,12 +11477,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -11842,11 +11487,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11961,17 +11601,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -11979,7 +11617,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11989,12 +11627,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -12004,11 +11637,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12123,17 +11751,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -12141,7 +11767,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12151,12 +11777,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -12166,11 +11787,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12285,17 +11901,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -12303,7 +11917,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12313,12 +11927,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -12328,11 +11937,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12591,17 +12195,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -12609,7 +12211,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12619,12 +12221,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -12634,11 +12231,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12753,17 +12345,15 @@
       <c r="O81" t="n">
         <v>2</v>
       </c>
+      <c r="P81" t="n">
+        <v>2</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -12771,7 +12361,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12781,12 +12371,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -12796,11 +12381,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12915,17 +12495,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -12933,7 +12511,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12943,12 +12521,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -12958,11 +12531,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13077,17 +12645,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -13095,7 +12661,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13105,12 +12671,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -13120,11 +12681,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13239,17 +12795,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -13257,7 +12811,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13267,12 +12821,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -13282,11 +12831,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13545,17 +13089,15 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -13563,7 +13105,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13573,12 +13115,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -13588,11 +13125,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13707,17 +13239,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -13725,7 +13255,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13735,12 +13265,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -13750,11 +13275,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13869,17 +13389,15 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
+      <c r="P88" t="n">
+        <v>2</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -13887,7 +13405,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13897,12 +13415,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -13912,11 +13425,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14031,17 +13539,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -14049,7 +13555,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14059,12 +13565,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -14074,11 +13575,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14337,17 +13833,15 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -14355,7 +13849,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14365,12 +13859,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -14380,11 +13869,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14499,17 +13983,15 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -14517,7 +13999,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14527,12 +14009,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -14542,11 +14019,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14661,17 +14133,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -14679,7 +14149,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14689,12 +14159,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -14704,11 +14169,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14823,17 +14283,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -14841,7 +14299,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14851,12 +14309,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -14866,11 +14319,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15129,17 +14577,15 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -15147,7 +14593,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15157,12 +14603,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -15172,11 +14613,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15291,17 +14727,15 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -15309,7 +14743,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15319,12 +14753,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -15334,11 +14763,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15453,17 +14877,15 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
+      <c r="P98" t="n">
+        <v>1</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -15471,7 +14893,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15481,12 +14903,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -15496,11 +14913,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15615,17 +15027,15 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -15633,7 +15043,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15643,12 +15053,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15658,11 +15063,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15777,17 +15177,15 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
+      <c r="P100" t="n">
+        <v>1</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -15795,7 +15193,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -15805,12 +15203,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -15820,11 +15213,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -16083,17 +15471,15 @@
       <c r="O102" t="n">
         <v>3</v>
       </c>
+      <c r="P102" t="n">
+        <v>3</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -16101,7 +15487,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16111,12 +15497,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -16126,11 +15507,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16245,17 +15621,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -16263,7 +15637,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16273,12 +15647,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -16288,11 +15657,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16407,17 +15771,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -16425,7 +15787,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16435,12 +15797,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16450,11 +15807,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16569,17 +15921,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -16587,7 +15937,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -16597,12 +15947,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -16612,11 +15957,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16875,17 +16215,15 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -16893,7 +16231,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -16903,12 +16241,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -16918,11 +16251,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -17037,17 +16365,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -17055,7 +16381,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17065,12 +16391,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -17080,11 +16401,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17199,17 +16515,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -17217,7 +16531,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17227,12 +16541,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -17242,11 +16551,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17361,17 +16665,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -17379,7 +16681,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17389,12 +16691,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -17404,11 +16701,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17523,17 +16815,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -17541,7 +16831,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -17551,12 +16841,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -17566,11 +16851,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17829,17 +17109,15 @@
       <c r="O113" t="n">
         <v>2</v>
       </c>
+      <c r="P113" t="n">
+        <v>2</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -17847,7 +17125,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -17857,12 +17135,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -17872,11 +17145,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17991,17 +17259,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -18009,7 +17275,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18019,12 +17285,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -18034,11 +17295,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -18153,17 +17409,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -18171,7 +17425,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18181,12 +17435,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -18196,11 +17445,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18315,17 +17559,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -18333,7 +17575,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -18343,12 +17585,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -18358,11 +17595,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18621,17 +17853,15 @@
       <c r="O118" t="n">
         <v>2</v>
       </c>
+      <c r="P118" t="n">
+        <v>2</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -18639,7 +17869,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -18649,12 +17879,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -18664,11 +17889,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18783,17 +18003,15 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -18801,7 +18019,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18811,12 +18029,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -18826,11 +18039,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18945,17 +18153,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -18963,7 +18169,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18973,12 +18179,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -18988,11 +18189,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -19107,17 +18303,15 @@
       <c r="O121" t="n">
         <v>2</v>
       </c>
+      <c r="P121" t="n">
+        <v>2</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -19125,7 +18319,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -19135,12 +18329,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -19150,11 +18339,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19557,17 +18741,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -19575,7 +18757,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -19585,12 +18767,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -19600,11 +18777,6 @@
       </c>
       <c r="AT124" t="n">
         <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19719,17 +18891,15 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -19737,7 +18907,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -19747,12 +18917,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -19762,11 +18927,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19881,17 +19041,15 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -19899,7 +19057,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -19909,12 +19067,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -19924,11 +19077,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -20043,17 +19191,15 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -20061,7 +19207,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -20071,12 +19217,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -20086,11 +19227,6 @@
       </c>
       <c r="AT127" t="n">
         <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -20205,17 +19341,15 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -20223,7 +19357,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20233,12 +19367,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
@@ -20248,11 +19377,6 @@
       </c>
       <c r="AT128" t="n">
         <v>1</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20511,17 +19635,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -20529,7 +19651,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20539,12 +19661,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -20554,11 +19671,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20673,17 +19785,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -20691,7 +19801,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -20701,12 +19811,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -20716,11 +19821,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20835,17 +19935,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -20853,7 +19951,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20863,12 +19961,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -20878,11 +19971,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20997,17 +20085,15 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -21015,7 +20101,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -21025,12 +20111,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
@@ -21040,11 +20121,6 @@
       </c>
       <c r="AT133" t="n">
         <v>1</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -21303,17 +20379,15 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -21321,7 +20395,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21331,12 +20405,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -21346,11 +20415,6 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21465,17 +20529,15 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -21483,7 +20545,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -21493,12 +20555,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -21508,11 +20565,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21627,17 +20679,15 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
+      <c r="P137" t="n">
+        <v>1</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -21645,7 +20695,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -21655,12 +20705,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -21670,11 +20715,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21789,17 +20829,15 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
+      <c r="P138" t="n">
+        <v>1</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -21807,7 +20845,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -21817,12 +20855,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -21832,11 +20865,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -22095,17 +21123,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -22113,7 +21139,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -22123,12 +21149,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -22138,11 +21159,6 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -22257,17 +21273,15 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
+      <c r="P141" t="n">
+        <v>1</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -22275,7 +21289,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -22285,12 +21299,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -22300,11 +21309,6 @@
       </c>
       <c r="AT141" t="n">
         <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22419,17 +21423,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -22437,7 +21439,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -22447,12 +21449,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -22462,11 +21459,6 @@
       </c>
       <c r="AT142" t="n">
         <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22581,17 +21573,15 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -22599,7 +21589,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -22609,12 +21599,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -22624,11 +21609,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22887,17 +21867,15 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -22905,7 +21883,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -22915,12 +21893,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -22930,11 +21903,6 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -23049,17 +22017,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -23067,7 +22033,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -23077,12 +22043,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -23092,11 +22053,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -23211,17 +22167,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -23229,7 +22183,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -23239,12 +22193,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -23254,11 +22203,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -23373,17 +22317,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -23391,7 +22333,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -23401,12 +22343,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -23416,11 +22353,6 @@
       </c>
       <c r="AT148" t="n">
         <v>1</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23535,17 +22467,15 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
+      <c r="P149" t="n">
+        <v>2</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -23553,7 +22483,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -23563,12 +22493,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -23578,11 +22503,6 @@
       </c>
       <c r="AT149" t="n">
         <v>1</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23841,17 +22761,15 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
+      <c r="P151" t="n">
+        <v>2</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -23859,7 +22777,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -23869,12 +22787,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -23884,11 +22797,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -24003,17 +22911,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -24021,7 +22927,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -24031,12 +22937,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -24046,11 +22947,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -24165,17 +23061,15 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -24183,7 +23077,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -24193,12 +23087,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -24208,11 +23097,6 @@
       </c>
       <c r="AT153" t="n">
         <v>1</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -24327,17 +23211,15 @@
       <c r="O154" t="n">
         <v>2</v>
       </c>
+      <c r="P154" t="n">
+        <v>2</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -24345,7 +23227,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -24355,12 +23237,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -24370,11 +23247,6 @@
       </c>
       <c r="AT154" t="n">
         <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24633,17 +23505,15 @@
       <c r="O156" t="n">
         <v>2</v>
       </c>
+      <c r="P156" t="n">
+        <v>2</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -24651,7 +23521,7 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -24661,12 +23531,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
@@ -24676,11 +23541,6 @@
       </c>
       <c r="AT156" t="n">
         <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24795,17 +23655,15 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
+      <c r="P157" t="n">
+        <v>1</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -24813,7 +23671,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -24823,12 +23681,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -24838,11 +23691,6 @@
       </c>
       <c r="AT157" t="n">
         <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24957,17 +23805,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -24975,7 +23821,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -24985,12 +23831,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -25000,11 +23841,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -25119,17 +23955,15 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -25137,7 +23971,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -25147,12 +23981,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -25162,11 +23991,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -25281,17 +24105,15 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -25299,7 +24121,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -25309,12 +24131,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -25324,11 +24141,6 @@
       </c>
       <c r="AT160" t="n">
         <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25587,17 +24399,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -25605,7 +24415,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -25615,12 +24425,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -25630,11 +24435,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25749,17 +24549,15 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -25767,7 +24565,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -25777,12 +24575,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -25792,11 +24585,6 @@
       </c>
       <c r="AT163" t="n">
         <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25911,17 +24699,15 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
+      <c r="P164" t="n">
+        <v>1</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -25929,7 +24715,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -25939,12 +24725,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -25954,11 +24735,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -26073,17 +24849,15 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -26091,7 +24865,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -26101,12 +24875,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -26116,11 +24885,6 @@
       </c>
       <c r="AT165" t="n">
         <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -26379,17 +25143,15 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
+      <c r="P167" t="n">
+        <v>1</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -26397,7 +25159,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -26407,12 +25169,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -26422,11 +25179,6 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26541,17 +25293,15 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -26559,7 +25309,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -26569,12 +25319,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -26584,11 +25329,6 @@
       </c>
       <c r="AT168" t="n">
         <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26703,17 +25443,15 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
+      <c r="P169" t="n">
+        <v>1</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -26721,7 +25459,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -26731,12 +25469,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -26746,11 +25479,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26865,17 +25593,15 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
+      <c r="P170" t="n">
+        <v>1</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -26883,7 +25609,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -26893,12 +25619,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -26908,11 +25629,6 @@
       </c>
       <c r="AT170" t="n">
         <v>1</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -27171,17 +25887,15 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -27189,7 +25903,7 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -27199,12 +25913,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
@@ -27214,11 +25923,6 @@
       </c>
       <c r="AT172" t="n">
         <v>1</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -27333,17 +26037,15 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -27351,7 +26053,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -27361,12 +26063,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
@@ -27376,11 +26073,6 @@
       </c>
       <c r="AT173" t="n">
         <v>1</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -27495,17 +26187,15 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -27513,7 +26203,7 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -27523,12 +26213,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
@@ -27538,11 +26223,6 @@
       </c>
       <c r="AT174" t="n">
         <v>1</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27657,17 +26337,15 @@
       <c r="O175" t="n">
         <v>2</v>
       </c>
+      <c r="P175" t="n">
+        <v>2</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -27675,7 +26353,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -27685,12 +26363,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -27700,11 +26373,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -27819,17 +26487,15 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -27837,7 +26503,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -27847,12 +26513,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -27862,11 +26523,6 @@
       </c>
       <c r="AT176" t="n">
         <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -28125,17 +26781,15 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -28143,7 +26797,7 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -28153,12 +26807,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
@@ -28168,11 +26817,6 @@
       </c>
       <c r="AT178" t="n">
         <v>1</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -28287,17 +26931,15 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
+      <c r="P179" t="n">
+        <v>1</v>
+      </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -28305,7 +26947,7 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -28315,12 +26957,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
@@ -28330,11 +26967,6 @@
       </c>
       <c r="AT179" t="n">
         <v>1</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -28449,17 +27081,15 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -28467,7 +27097,7 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -28477,12 +27107,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
@@ -28492,11 +27117,6 @@
       </c>
       <c r="AT180" t="n">
         <v>1</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -28611,17 +27231,15 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
+      <c r="P181" t="n">
+        <v>1</v>
+      </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -28629,7 +27247,7 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -28639,12 +27257,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
@@ -28654,11 +27267,6 @@
       </c>
       <c r="AT181" t="n">
         <v>1</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -28917,17 +27525,15 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -28935,7 +27541,7 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -28945,12 +27551,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
@@ -28960,11 +27561,6 @@
       </c>
       <c r="AT183" t="n">
         <v>1</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -29079,17 +27675,15 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -29097,7 +27691,7 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -29107,12 +27701,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
@@ -29122,11 +27711,6 @@
       </c>
       <c r="AT184" t="n">
         <v>1</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -29241,17 +27825,15 @@
       <c r="O185" t="n">
         <v>2</v>
       </c>
+      <c r="P185" t="n">
+        <v>2</v>
+      </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -29259,7 +27841,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -29269,12 +27851,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
@@ -29284,11 +27861,6 @@
       </c>
       <c r="AT185" t="n">
         <v>1</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -29403,17 +27975,15 @@
       <c r="O186" t="n">
         <v>2</v>
       </c>
+      <c r="P186" t="n">
+        <v>2</v>
+      </c>
       <c r="Q186" t="n">
         <v>0</v>
       </c>
       <c r="R186" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>HOLD_JP_83abc419039df1884eba8e14634d</t>
@@ -29421,7 +27991,7 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -29431,12 +28001,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
@@ -29446,11 +28011,6 @@
       </c>
       <c r="AT186" t="n">
         <v>1</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
